--- a/database.xlsx
+++ b/database.xlsx
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9229</v>
+        <v>8829</v>
       </c>
       <c r="C2" t="n">
-        <v>12139</v>
+        <v>12119</v>
       </c>
     </row>
     <row r="3">
